--- a/الخدمات.xlsx
+++ b/الخدمات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a843af4fc71c607/Desktop/JavaScript codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3056" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54744602-4097-4578-87A9-52B8F9234DC7}"/>
+  <xr:revisionPtr revIDLastSave="3102" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD261AB0-E638-4589-BB01-24243FD3B7C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="482">
   <si>
     <t>ت.</t>
   </si>
@@ -1453,6 +1453,36 @@
   </si>
   <si>
     <t>تخفيض أجور</t>
+  </si>
+  <si>
+    <t>كبار المكلفين- التحاسب الضريبي</t>
+  </si>
+  <si>
+    <t>التحاسب الضريبي</t>
+  </si>
+  <si>
+    <t>منصة كبار المكلفين - عدم الممانعة</t>
+  </si>
+  <si>
+    <t>عدم الممانعة</t>
+  </si>
+  <si>
+    <t>تقديم طلب إلكتروني بخصوص معاملات الأموال المنقولة وغير المنقولة للقاصرين</t>
+  </si>
+  <si>
+    <t>معاملات الأموال</t>
+  </si>
+  <si>
+    <t>التقديم على فريضة الحج للمشمولين بقانون مؤسسة السجناء السياسيين لسنة 2027</t>
+  </si>
+  <si>
+    <t>فريضة الحج</t>
+  </si>
+  <si>
+    <t>تقديم طلب إلكتروني للإستثمار في المناطق الحرة</t>
+  </si>
+  <si>
+    <t>المناطق الحرة</t>
   </si>
 </sst>
 </file>
@@ -1502,7 +1532,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1606,12 +1636,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1674,22 +1739,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="58">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="57">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3130,39 +3200,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G218" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G223" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55">
+  <autoFilter ref="A1:G223" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G210">
     <sortCondition ref="B2:B210"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="53" totalsRowDxfId="52">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="51" totalsRowDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="41" totalsRowDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="40" dataDxfId="38" totalsRowDxfId="37" headerRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="39" dataDxfId="37" totalsRowDxfId="36" headerRowBorderDxfId="38">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I8">
     <sortCondition ref="G2:G8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="36" totalsRowDxfId="35">
+    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
+    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="30" totalsRowDxfId="29" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Percent">
       <calculatedColumnFormula>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3171,19 +3242,19 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
     <sortCondition ref="B2:B41"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="23" totalsRowDxfId="22">
+    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17">
       <calculatedColumnFormula>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3192,16 +3263,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="10" totalsRowDxfId="9">
+    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>ROW()-11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5">
+    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="4" totalsRowDxfId="3" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Percent">
       <calculatedColumnFormula>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3472,7 +3543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -8693,22 +8764,142 @@
     </row>
     <row r="218" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A218:A223" si="5">ROW()-1</f>
         <v>217</v>
       </c>
-      <c r="B218" s="3"/>
-      <c r="C218" s="3"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-      <c r="F218" s="3"/>
-      <c r="G218" s="3"/>
+      <c r="B218" s="3">
+        <v>21553</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A219" s="3">
+        <f t="shared" si="5"/>
+        <v>218</v>
+      </c>
+      <c r="B219" s="3">
+        <v>21563</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A220" s="3">
+        <f t="shared" si="5"/>
+        <v>219</v>
+      </c>
+      <c r="B220" s="3">
+        <v>21075</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A221" s="3">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="B221" s="3">
+        <v>21858</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A222" s="3">
+        <f t="shared" si="5"/>
+        <v>221</v>
+      </c>
+      <c r="B222" s="3">
+        <v>10509</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A223" s="3">
+        <f t="shared" si="5"/>
+        <v>222</v>
+      </c>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
+      <c r="E223" s="3"/>
+      <c r="F223" s="3"/>
+      <c r="G223" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B218">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  <conditionalFormatting sqref="B2:B223">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8743,11 +8934,11 @@
       <c r="C1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="18"/>
+      <c r="F1" s="25" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -8772,12 +8963,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>2</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="23">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.2592592592592587E-3</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="2">
+        <v>9.0497737556561094E-3</v>
+      </c>
+      <c r="E2" s="18"/>
+      <c r="F2" s="25">
         <f t="shared" ref="F2:F8" si="1">ROW()-1</f>
         <v>1</v>
       </c>
@@ -8790,7 +8981,7 @@
       </c>
       <c r="I2" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.7777777777777776E-2</v>
+        <v>2.7149321266968326E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -8805,12 +8996,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>5</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.3148148148148147E-2</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+        <v>2.2624434389140271E-2</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="25">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -8823,7 +9014,7 @@
       </c>
       <c r="I3" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>9.2592592592592587E-3</v>
+        <v>9.0497737556561094E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -8838,12 +9029,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>16</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>7.407407407407407E-2</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+        <v>7.2398190045248875E-2</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="25">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -8856,7 +9047,7 @@
       </c>
       <c r="I4" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -8871,12 +9062,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>2</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.2592592592592587E-3</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+        <v>9.0497737556561094E-3</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="25">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -8889,7 +9080,7 @@
       </c>
       <c r="I5" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.20370370370370369</v>
+        <v>0.19909502262443438</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -8904,12 +9095,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>4</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8518518518518517E-2</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+        <v>1.8099547511312219E-2</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="25">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -8918,11 +9109,11 @@
       </c>
       <c r="H6" s="2">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
+        <v>1.8099547511312219E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -8937,12 +9128,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>3</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="8">
+        <v>1.3574660633484163E-2</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -8955,7 +9146,7 @@
       </c>
       <c r="I7" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.1111111111111111</v>
+        <v>0.10859728506787331</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -8970,12 +9161,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>1</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
+        <v>4.5248868778280547E-3</v>
       </c>
       <c r="E8" s="18"/>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -8984,11 +9175,11 @@
       </c>
       <c r="H8" s="8">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I8" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.62037037037037035</v>
+        <v>0.6244343891402715</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9003,18 +9194,18 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>1</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="17"/>
+        <v>4.5248868778280547E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="26"/>
       <c r="G9" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="17">
         <f>SUBTOTAL(109,Table2[عدد الخدمات])</f>
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I9" s="21"/>
     </row>
@@ -9030,12 +9221,12 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>13</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>6.0185185185185182E-2</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -9052,11 +9243,11 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>1</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>4.5248868778280547E-3</v>
+      </c>
+      <c r="E11" s="18"/>
       <c r="F11" s="9" t="s">
         <v>90</v>
       </c>
@@ -9082,11 +9273,11 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>2</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.2592592592592587E-3</v>
-      </c>
-      <c r="E12" s="7"/>
+        <v>9.0497737556561094E-3</v>
+      </c>
+      <c r="E12" s="18"/>
       <c r="F12" s="12">
         <v>1</v>
       </c>
@@ -9099,7 +9290,7 @@
       </c>
       <c r="I12" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>7.8703703703703706E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9114,9 +9305,9 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>3</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="12">
@@ -9127,11 +9318,11 @@
       </c>
       <c r="H13" s="13">
         <f>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</f>
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I13" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>0.92129629629629628</v>
+        <v>0.92307692307692313</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9146,18 +9337,18 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>2</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.2592592592592587E-3</v>
-      </c>
-      <c r="E14" s="5"/>
+        <v>9.0497737556561094E-3</v>
+      </c>
+      <c r="E14" s="18"/>
       <c r="F14" s="12"/>
       <c r="G14" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="13">
         <f>SUBTOTAL(109,Table4[عدد الخدمات])</f>
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -9173,11 +9364,11 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>1</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
-      </c>
-      <c r="E15" s="7"/>
+        <v>4.5248868778280547E-3</v>
+      </c>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
@@ -9191,9 +9382,9 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>16</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>7.407407407407407E-2</v>
+        <v>7.2398190045248875E-2</v>
       </c>
       <c r="E16" s="18"/>
     </row>
@@ -9209,11 +9400,11 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>1</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
-      </c>
-      <c r="E17" s="7"/>
+        <v>4.5248868778280547E-3</v>
+      </c>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
@@ -9227,9 +9418,9 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>3</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
       <c r="E18" s="18"/>
     </row>
@@ -9243,11 +9434,11 @@
       </c>
       <c r="C19" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>3</v>
-      </c>
-      <c r="D19" s="19">
+        <v>4</v>
+      </c>
+      <c r="D19" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
+        <v>1.8099547511312219E-2</v>
       </c>
       <c r="E19" s="18"/>
     </row>
@@ -9263,9 +9454,9 @@
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
         <v>1</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
+        <v>4.5248868778280547E-3</v>
       </c>
       <c r="E20" s="18"/>
     </row>
@@ -9283,7 +9474,7 @@
       </c>
       <c r="D21" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.2592592592592587E-3</v>
+        <v>9.0497737556561094E-3</v>
       </c>
       <c r="E21" s="18"/>
     </row>
@@ -9301,7 +9492,7 @@
       </c>
       <c r="D22" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
+        <v>4.5248868778280547E-3</v>
       </c>
       <c r="E22" s="18"/>
     </row>
@@ -9319,7 +9510,7 @@
       </c>
       <c r="D23" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.2407407407407406E-2</v>
+        <v>3.1674208144796379E-2</v>
       </c>
       <c r="E23" s="18"/>
     </row>
@@ -9337,7 +9528,7 @@
       </c>
       <c r="D24" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.7777777777777776E-2</v>
+        <v>2.7149321266968326E-2</v>
       </c>
       <c r="E24" s="18"/>
     </row>
@@ -9355,7 +9546,7 @@
       </c>
       <c r="D25" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.7037037037037035E-2</v>
+        <v>3.6199095022624438E-2</v>
       </c>
       <c r="E25" s="18"/>
     </row>
@@ -9373,7 +9564,7 @@
       </c>
       <c r="D26" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10185185185185185</v>
+        <v>9.9547511312217188E-2</v>
       </c>
       <c r="E26" s="18"/>
     </row>
@@ -9391,7 +9582,7 @@
       </c>
       <c r="D27" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
+        <v>4.5248868778280547E-3</v>
       </c>
       <c r="E27" s="18"/>
     </row>
@@ -9409,7 +9600,7 @@
       </c>
       <c r="D28" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.1666666666666664E-2</v>
+        <v>4.072398190045249E-2</v>
       </c>
       <c r="E28" s="18"/>
     </row>
@@ -9427,7 +9618,7 @@
       </c>
       <c r="D29" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.3148148148148147E-2</v>
+        <v>2.2624434389140271E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" x14ac:dyDescent="0.3">
@@ -9444,7 +9635,7 @@
       </c>
       <c r="D30" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8518518518518517E-2</v>
+        <v>1.8099547511312219E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.3">
@@ -9461,7 +9652,7 @@
       </c>
       <c r="D31" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" x14ac:dyDescent="0.3">
@@ -9478,7 +9669,7 @@
       </c>
       <c r="D32" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8518518518518517E-2</v>
+        <v>1.8099547511312219E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9495,7 +9686,7 @@
       </c>
       <c r="D33" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3888888888888888E-2</v>
+        <v>1.3574660633484163E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9508,11 +9699,11 @@
       </c>
       <c r="C34" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.1666666666666664E-2</v>
+        <v>4.5248868778280542E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9529,7 +9720,7 @@
       </c>
       <c r="D35" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.2592592592592587E-3</v>
+        <v>9.0497737556561094E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9546,7 +9737,7 @@
       </c>
       <c r="D36" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
+        <v>4.5248868778280547E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9559,11 +9750,11 @@
       </c>
       <c r="C37" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.7777777777777776E-2</v>
+        <v>4.072398190045249E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9580,7 +9771,7 @@
       </c>
       <c r="D38" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.1666666666666664E-2</v>
+        <v>4.072398190045249E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9597,7 +9788,7 @@
       </c>
       <c r="D39" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-2</v>
+        <v>4.5248868778280542E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9614,7 +9805,7 @@
       </c>
       <c r="D40" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.6296296296296294E-3</v>
+        <v>4.5248868778280547E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9631,7 +9822,7 @@
       </c>
       <c r="D41" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10648148148148148</v>
+        <v>0.10407239819004525</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9641,11 +9832,11 @@
       </c>
       <c r="C42" s="8">
         <f>SUBTOTAL(109,Table3[عدد الخدمات])</f>
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D42" s="20">
         <f>SUBTOTAL(109,Table3[النسبة المئوية])</f>
-        <v>0.99999999999999989</v>
+        <v>0.99999999999999978</v>
       </c>
     </row>
   </sheetData>

--- a/الخدمات.xlsx
+++ b/الخدمات.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a843af4fc71c607/Desktop/JavaScript codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3102" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD261AB0-E638-4589-BB01-24243FD3B7C2}"/>
+  <xr:revisionPtr revIDLastSave="3169" documentId="11_6D1415C555E27CE26E339E56ADDC14C75C28AAF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5460B452-1C81-41FD-B34D-85B3EAE88424}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="496">
   <si>
     <t>ت.</t>
   </si>
@@ -1483,6 +1483,48 @@
   </si>
   <si>
     <t>المناطق الحرة</t>
+  </si>
+  <si>
+    <t>الاستعلام عن المجالس واللجان التحقيقية الخاصة بقضايا التحريف و ازدواجية الراتب</t>
+  </si>
+  <si>
+    <t>المجالس واللجان</t>
+  </si>
+  <si>
+    <t>استمارة تنفيذ مبادرات/ المجلس الوطني للشباب</t>
+  </si>
+  <si>
+    <t>تنفيذ مبادرات</t>
+  </si>
+  <si>
+    <t>استمارة حجز موعد</t>
+  </si>
+  <si>
+    <t>حجز موعد</t>
+  </si>
+  <si>
+    <t>الاستمارة الالكترونية لجمع بيانات الموظفين والكادر التدريسي لمديرية العامة لتربية الكرخ الاولى</t>
+  </si>
+  <si>
+    <t>جمع بيانات</t>
+  </si>
+  <si>
+    <t>الاستمارة الاكترونية الخاصة بجرد أجهزة الحاسوب وملحقاتها للمدارس التابعة لتربية بغداد الكرخ الاولى</t>
+  </si>
+  <si>
+    <t>أجهزة الحاسوب</t>
+  </si>
+  <si>
+    <t>اقسام وشعب</t>
+  </si>
+  <si>
+    <t>الاستمارة الالكترونية الخاصة بجرد أجهزة الحاسوب وملحقاتها لاقسام وشعب تربية بغداد الكرخ الاولى</t>
+  </si>
+  <si>
+    <t>توزيع قطع اراضي - عوائل شهداء الجيش الابيض (شهداء كورونا)</t>
+  </si>
+  <si>
+    <t>شهداء كورونا</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1801,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="58">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3200,40 +3252,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G223" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55">
-  <autoFilter ref="A1:G223" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G210">
-    <sortCondition ref="B2:B210"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F07007DD-6219-4111-BA74-4FEE49F84178}" name="Table1" displayName="Table1" ref="A1:G230" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G230">
+    <sortCondition ref="B2:B230"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="53" totalsRowDxfId="52">
+    <tableColumn id="1" xr3:uid="{20FD99FD-87DB-4DD1-989A-014AAE8F25F6}" name="ت." dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="51" totalsRowDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{F323E4AC-F323-4F97-9904-326D9949B165}" name="رقم الخدمة" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{58A3CC8C-66BF-4DA6-B0EF-C7F43089C5C0}" name="اسم الخدمة" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{176DB514-0824-46BC-9146-CAA89D7A742F}" name="جهة الخدمة" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{E4173C63-A839-4611-8E53-7B3AE2F439DB}" name="نوع الجهة" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{C01A4E12-3E16-4DE9-86B3-69F70894487E}" name="نوع العمل" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{3481871F-BF9F-4C45-AC54-67A9AF362483}" name="اسم الملف" dataDxfId="42" totalsRowDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="39" dataDxfId="37" totalsRowDxfId="36" headerRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C8B1F257-44EE-46D6-BF12-56DE95D1A039}" name="Table2" displayName="Table2" ref="F1:I9" totalsRowCount="1" headerRowDxfId="40" dataDxfId="38" totalsRowDxfId="37" headerRowBorderDxfId="39">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I8">
     <sortCondition ref="G2:G8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="1" xr3:uid="{FDC31943-D832-4BCF-8A6F-51F74847839D}" name="ت." dataDxfId="36" totalsRowDxfId="35">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="2" xr3:uid="{D6F61CFE-6FB5-4088-802C-280AB03DDC3F}" name="نوع الجهة" totalsRowLabel="المجموع" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{819F64F0-7B30-437C-8552-96E1BA009158}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
       <calculatedColumnFormula>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{D928E8D0-BE48-4700-B3FA-A3A0C6ED8D95}" name="النسبة المئوية" dataDxfId="30" totalsRowDxfId="29" dataCellStyle="Percent">
       <calculatedColumnFormula>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3242,19 +3293,19 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BF9702DE-766F-4CF2-9B1D-2C4151D8816A}" name="Table3" displayName="Table3" ref="A1:D42" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
     <sortCondition ref="B2:B41"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="1" xr3:uid="{04CB5523-1DF6-4CA0-AC24-1D21F85D9F94}" name="ت." dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17">
+    <tableColumn id="2" xr3:uid="{966ACB29-C086-4C8E-BD62-D0F9ECCCA301}" name="اسم الجهة" totalsRowLabel="المجموع" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{E47A3AE0-B7A7-44F8-8FA6-8FA757A3066F}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15" dataCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{0D34DEDD-061D-44F4-9DA6-86D41E4BDDB7}" name="النسبة المئوية" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Percent">
       <calculatedColumnFormula>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3263,16 +3314,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA56BF47-5D06-47A5-8205-AC117836580F}" name="Table4" displayName="Table4" ref="F11:I14" totalsRowCount="1" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="1" xr3:uid="{B2E7143D-F8BC-4FF5-B1BE-2A90C29EF400}" name="ت" dataDxfId="10" totalsRowDxfId="9">
       <calculatedColumnFormula>ROW()-11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="2" xr3:uid="{4A8E3EC9-46C6-46A2-85BB-E7D02B7ABF90}" name="نوع العمل" totalsRowLabel="المجموع" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{140AD779-6235-4A33-848F-7CF18BA55E33}" name="عدد الخدمات" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{CD921388-F9B8-4CDD-A07C-FBB8C0ABF589}" name="النسبة المئوية" dataDxfId="4" totalsRowDxfId="3" dataCellStyle="Percent">
       <calculatedColumnFormula>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3543,7 +3594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -3580,7 +3631,7 @@
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <f t="shared" ref="A2:A65" si="0">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -3604,7 +3655,7 @@
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="3">
@@ -3628,7 +3679,7 @@
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>3</v>
       </c>
       <c r="B4" s="3">
@@ -3652,7 +3703,7 @@
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>4</v>
       </c>
       <c r="B5" s="3">
@@ -3676,7 +3727,7 @@
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>5</v>
       </c>
       <c r="B6" s="3">
@@ -3700,7 +3751,7 @@
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>6</v>
       </c>
       <c r="B7" s="3">
@@ -3724,7 +3775,7 @@
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>7</v>
       </c>
       <c r="B8" s="3">
@@ -3748,7 +3799,7 @@
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>8</v>
       </c>
       <c r="B9" s="3">
@@ -3772,7 +3823,7 @@
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>9</v>
       </c>
       <c r="B10" s="3">
@@ -3796,7 +3847,7 @@
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>10</v>
       </c>
       <c r="B11" s="3">
@@ -3820,7 +3871,7 @@
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>11</v>
       </c>
       <c r="B12" s="3">
@@ -3844,7 +3895,7 @@
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>12</v>
       </c>
       <c r="B13" s="3">
@@ -3868,17 +3919,17 @@
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>10514</v>
+        <v>10509</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>37</v>
+        <v>480</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>7</v>
@@ -3887,43 +3938,43 @@
         <v>88</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>199</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>10532</v>
+        <v>10514</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="1">
-        <v>10532</v>
+      <c r="G15" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>10539</v>
+        <v>10532</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>79</v>
@@ -3935,19 +3986,19 @@
         <v>88</v>
       </c>
       <c r="G16" s="1">
-        <v>10539</v>
+        <v>10532</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>10541</v>
+        <v>10539</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>79</v>
@@ -3959,67 +4010,67 @@
         <v>88</v>
       </c>
       <c r="G17" s="1">
-        <v>10541</v>
+        <v>10539</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>10562</v>
+        <v>10541</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>192</v>
+      <c r="G18" s="1">
+        <v>10541</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>10565</v>
+        <v>10562</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="1">
-        <v>10565</v>
+      <c r="G19" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>10568</v>
+        <v>10565</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>79</v>
@@ -4031,46 +4082,46 @@
         <v>88</v>
       </c>
       <c r="G20" s="1">
-        <v>10568</v>
+        <v>10565</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>10579</v>
+        <v>10568</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>240</v>
+      <c r="G21" s="1">
+        <v>10568</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>10603</v>
+        <v>10579</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>444</v>
+        <v>97</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>7</v>
@@ -4079,43 +4130,43 @@
         <v>88</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>445</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>10611</v>
+        <v>10603</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>145</v>
+        <v>444</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="1">
-        <v>10611</v>
+      <c r="G23" s="1" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>10630</v>
+        <v>10611</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>79</v>
@@ -4127,46 +4178,46 @@
         <v>88</v>
       </c>
       <c r="G24" s="1">
-        <v>10630</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>10648</v>
+        <v>10630</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>232</v>
+      <c r="G25" s="1">
+        <v>10630</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>10664</v>
+        <v>10648</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>7</v>
@@ -4174,167 +4225,167 @@
       <c r="F26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G26" s="1">
-        <v>10664</v>
+      <c r="G26" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>10675</v>
+        <v>10664</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>200</v>
+        <v>88</v>
+      </c>
+      <c r="G27" s="1">
+        <v>10664</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>10688</v>
+        <v>10675</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="1">
-        <v>10688</v>
+        <v>89</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>10712</v>
+        <v>10688</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>360</v>
+        <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>361</v>
+      <c r="G29" s="1">
+        <v>10688</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>10715</v>
+        <v>10712</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>63</v>
+        <v>360</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>238</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>10727</v>
+        <v>10715</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>163</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>10730</v>
+        <v>10727</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>10756</v>
+        <v>10730</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>7</v>
@@ -4343,22 +4394,22 @@
         <v>88</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>10780</v>
+        <v>10756</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>65</v>
+        <v>403</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>7</v>
@@ -4367,163 +4418,163 @@
         <v>88</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>186</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>10876</v>
+        <v>10780</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>430</v>
+        <v>66</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>321</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>35</v>
       </c>
       <c r="B36" s="3">
-        <v>10884</v>
+        <v>10876</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>47</v>
+        <v>320</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>46</v>
+        <v>430</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>231</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>36</v>
       </c>
       <c r="B37" s="3">
-        <v>10913</v>
+        <v>10884</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>37</v>
       </c>
       <c r="B38" s="3">
-        <v>10928</v>
+        <v>10913</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>235</v>
+        <v>30</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>38</v>
       </c>
       <c r="B39" s="3">
-        <v>10930</v>
+        <v>10928</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>39</v>
       </c>
       <c r="B40" s="3">
-        <v>10935</v>
+        <v>10930</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>234</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>40</v>
       </c>
       <c r="B41" s="3">
-        <v>10947</v>
+        <v>10935</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>375</v>
+        <v>233</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>46</v>
@@ -4535,22 +4586,22 @@
         <v>88</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>376</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>41</v>
       </c>
       <c r="B42" s="3">
-        <v>10974</v>
+        <v>10947</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>93</v>
+        <v>375</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>7</v>
@@ -4559,22 +4610,22 @@
         <v>88</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>215</v>
+        <v>376</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>42</v>
       </c>
       <c r="B43" s="3">
-        <v>10979</v>
+        <v>10974</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>7</v>
@@ -4583,43 +4634,43 @@
         <v>88</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>43</v>
       </c>
       <c r="B44" s="3">
-        <v>10987</v>
+        <v>10979</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>170</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>44</v>
       </c>
       <c r="B45" s="3">
-        <v>10995</v>
+        <v>10987</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>22</v>
@@ -4631,70 +4682,70 @@
         <v>88</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>45</v>
       </c>
       <c r="B46" s="3">
-        <v>21020</v>
+        <v>10995</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>46</v>
       </c>
       <c r="B47" s="3">
-        <v>21058</v>
+        <v>21020</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>294</v>
+        <v>33</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>187</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>47</v>
       </c>
       <c r="B48" s="3">
-        <v>21063</v>
+        <v>21058</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>117</v>
+        <v>294</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>7</v>
@@ -4703,214 +4754,214 @@
         <v>88</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>48</v>
       </c>
       <c r="B49" s="3">
-        <v>21064</v>
+        <v>21063</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>49</v>
       </c>
       <c r="B50" s="3">
-        <v>21067</v>
+        <v>21064</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>154</v>
+        <v>11</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>50</v>
       </c>
       <c r="B51" s="3">
-        <v>21070</v>
+        <v>21067</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>51</v>
       </c>
       <c r="B52" s="3">
-        <v>21071</v>
+        <v>21070</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>52</v>
       </c>
       <c r="B53" s="3">
-        <v>21076</v>
+        <v>21071</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G53" s="1">
-        <v>21076</v>
+      <c r="G53" s="1" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>53</v>
       </c>
       <c r="B54" s="3">
-        <v>21078</v>
+        <v>21075</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>8</v>
+        <v>476</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>179</v>
+        <v>477</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>54</v>
       </c>
       <c r="B55" s="3">
-        <v>21093</v>
+        <v>21076</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>218</v>
+      <c r="G55" s="1">
+        <v>21076</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>55</v>
       </c>
       <c r="B56" s="3">
-        <v>21097</v>
+        <v>21078</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>56</v>
       </c>
       <c r="B57" s="3">
-        <v>21098</v>
+        <v>21093</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>301</v>
+        <v>85</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>7</v>
@@ -4919,70 +4970,70 @@
         <v>88</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>302</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>57</v>
       </c>
       <c r="B58" s="3">
-        <v>21102</v>
+        <v>21097</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>58</v>
       </c>
       <c r="B59" s="3">
-        <v>21116</v>
+        <v>21098</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>59</v>
       </c>
       <c r="B60" s="3">
-        <v>21126</v>
+        <v>21102</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>7</v>
@@ -4991,403 +5042,403 @@
         <v>88</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>60</v>
       </c>
       <c r="B61" s="3">
-        <v>21151</v>
+        <v>21116</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>54</v>
+        <v>266</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>61</v>
       </c>
       <c r="B62" s="3">
-        <v>21179</v>
+        <v>21126</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>62</v>
       </c>
       <c r="B63" s="3">
-        <v>21184</v>
+        <v>21151</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>63</v>
       </c>
       <c r="B64" s="3">
-        <v>21185</v>
+        <v>21179</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>64</v>
       </c>
       <c r="B65" s="3">
-        <v>21186</v>
+        <v>21184</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>39</v>
+        <v>260</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <f t="shared" ref="A66:A129" si="1">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>65</v>
       </c>
       <c r="B66" s="3">
-        <v>21193</v>
+        <v>21185</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>159</v>
+        <v>258</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>66</v>
       </c>
       <c r="B67" s="3">
-        <v>21195</v>
+        <v>21186</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>67</v>
       </c>
       <c r="B68" s="3">
-        <v>21196</v>
+        <v>21193</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>68</v>
       </c>
       <c r="B69" s="3">
-        <v>21209</v>
+        <v>21195</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>69</v>
       </c>
       <c r="B70" s="3">
-        <v>21216</v>
+        <v>21196</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>436</v>
+        <v>57</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>437</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>70</v>
       </c>
       <c r="B71" s="3">
-        <v>21218</v>
+        <v>21209</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>71</v>
       </c>
       <c r="B72" s="3">
-        <v>21219</v>
+        <v>21216</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>28</v>
+        <v>436</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>259</v>
+        <v>437</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>72</v>
       </c>
       <c r="B73" s="3">
-        <v>21220</v>
+        <v>21218</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>73</v>
       </c>
       <c r="B74" s="3">
-        <v>21222</v>
+        <v>21219</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>74</v>
       </c>
       <c r="B75" s="3">
-        <v>21226</v>
+        <v>21220</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>255</v>
+        <v>61</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>75</v>
       </c>
       <c r="B76" s="3">
-        <v>21228</v>
+        <v>21222</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>239</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>76</v>
       </c>
       <c r="B77" s="3">
-        <v>21241</v>
+        <v>21226</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>131</v>
+        <v>255</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>24</v>
@@ -5396,49 +5447,49 @@
         <v>7</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>77</v>
       </c>
       <c r="B78" s="3">
-        <v>21242</v>
+        <v>21228</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>78</v>
       </c>
       <c r="B79" s="3">
-        <v>21247</v>
+        <v>21241</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>7</v>
@@ -5447,70 +5498,70 @@
         <v>88</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>79</v>
       </c>
       <c r="B80" s="3">
-        <v>21261</v>
+        <v>21242</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>284</v>
+        <v>121</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>285</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>80</v>
       </c>
       <c r="B81" s="3">
-        <v>21264</v>
+        <v>21247</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>81</v>
       </c>
       <c r="B82" s="3">
-        <v>21305</v>
+        <v>21261</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>48</v>
+        <v>284</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>7</v>
@@ -5519,118 +5570,118 @@
         <v>88</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>82</v>
       </c>
       <c r="B83" s="3">
-        <v>21311</v>
+        <v>21264</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>83</v>
       </c>
       <c r="B84" s="3">
-        <v>21312</v>
+        <v>21305</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>84</v>
       </c>
       <c r="B85" s="3">
-        <v>21323</v>
+        <v>21311</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>297</v>
+        <v>96</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>298</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>85</v>
       </c>
       <c r="B86" s="3">
-        <v>21324</v>
+        <v>21312</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>295</v>
+        <v>23</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>296</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>86</v>
       </c>
       <c r="B87" s="3">
-        <v>21325</v>
+        <v>21323</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>17</v>
+        <v>297</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>10</v>
@@ -5639,91 +5690,91 @@
         <v>88</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>178</v>
+        <v>298</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>87</v>
       </c>
       <c r="B88" s="3">
-        <v>21331</v>
+        <v>21324</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>88</v>
       </c>
       <c r="B89" s="3">
-        <v>21337</v>
+        <v>21325</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>89</v>
       </c>
       <c r="B90" s="3">
-        <v>21343</v>
+        <v>21331</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>353</v>
+        <v>269</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>354</v>
+        <v>58</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>355</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>90</v>
       </c>
       <c r="B91" s="3">
-        <v>21356</v>
+        <v>21337</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>24</v>
@@ -5735,67 +5786,67 @@
         <v>89</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>91</v>
       </c>
       <c r="B92" s="3">
-        <v>21374</v>
+        <v>21343</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>31</v>
+        <v>353</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>24</v>
+        <v>354</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>264</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>92</v>
       </c>
       <c r="B93" s="3">
-        <v>21377</v>
+        <v>21356</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>93</v>
       </c>
       <c r="B94" s="3">
-        <v>21378</v>
+        <v>21374</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>24</v>
@@ -5807,22 +5858,22 @@
         <v>89</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>94</v>
       </c>
       <c r="B95" s="3">
-        <v>21381</v>
+        <v>21377</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>7</v>
@@ -5831,46 +5882,46 @@
         <v>88</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>95</v>
       </c>
       <c r="B96" s="3">
-        <v>21390</v>
+        <v>21378</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>96</v>
       </c>
       <c r="B97" s="3">
-        <v>21391</v>
+        <v>21381</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>282</v>
+        <v>151</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>7</v>
@@ -5879,22 +5930,22 @@
         <v>88</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>283</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>97</v>
       </c>
       <c r="B98" s="3">
-        <v>21395</v>
+        <v>21390</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>7</v>
@@ -5903,142 +5954,142 @@
         <v>88</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>98</v>
       </c>
       <c r="B99" s="3">
-        <v>21404</v>
+        <v>21391</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>94</v>
+        <v>282</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>166</v>
+        <v>283</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>99</v>
       </c>
       <c r="B100" s="3">
-        <v>21405</v>
+        <v>21395</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>100</v>
       </c>
       <c r="B101" s="3">
-        <v>21407</v>
+        <v>21404</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>430</v>
+        <v>95</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>101</v>
       </c>
       <c r="B102" s="3">
-        <v>21409</v>
+        <v>21405</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>102</v>
       </c>
       <c r="B103" s="3">
-        <v>21411</v>
+        <v>21407</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>35</v>
+        <v>430</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>103</v>
       </c>
       <c r="B104" s="3">
-        <v>21412</v>
+        <v>21409</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>7</v>
@@ -6047,19 +6098,19 @@
         <v>88</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>104</v>
       </c>
       <c r="B105" s="3">
-        <v>21413</v>
+        <v>21411</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>101</v>
+        <v>338</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>35</v>
@@ -6071,22 +6122,22 @@
         <v>88</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>204</v>
+        <v>339</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>105</v>
       </c>
       <c r="B106" s="3">
-        <v>21422</v>
+        <v>21412</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>442</v>
+        <v>34</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>7</v>
@@ -6095,22 +6146,22 @@
         <v>88</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>443</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>106</v>
       </c>
       <c r="B107" s="3">
-        <v>21424</v>
+        <v>21413</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>7</v>
@@ -6119,22 +6170,22 @@
         <v>88</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>112</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>107</v>
       </c>
       <c r="B108" s="3">
-        <v>21425</v>
+        <v>21422</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>111</v>
+        <v>442</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>7</v>
@@ -6143,43 +6194,43 @@
         <v>88</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>189</v>
+        <v>443</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>108</v>
       </c>
       <c r="B109" s="3">
-        <v>21431</v>
+        <v>21424</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>109</v>
       </c>
       <c r="B110" s="3">
-        <v>21433</v>
+        <v>21425</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>70</v>
@@ -6191,115 +6242,115 @@
         <v>88</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>110</v>
       </c>
       <c r="B111" s="3">
-        <v>21439</v>
+        <v>21431</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>111</v>
       </c>
       <c r="B112" s="3">
-        <v>21442</v>
+        <v>21433</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>112</v>
       </c>
       <c r="B113" s="3">
-        <v>21445</v>
+        <v>21439</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>113</v>
       </c>
       <c r="B114" s="3">
-        <v>21448</v>
+        <v>21442</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>114</v>
       </c>
       <c r="B115" s="3">
-        <v>21449</v>
+        <v>21445</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>58</v>
@@ -6308,49 +6359,49 @@
         <v>7</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>115</v>
       </c>
       <c r="B116" s="3">
-        <v>21451</v>
+        <v>21448</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>430</v>
+        <v>58</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>116</v>
       </c>
       <c r="B117" s="3">
-        <v>21453</v>
+        <v>21449</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>127</v>
+        <v>212</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>7</v>
@@ -6359,46 +6410,46 @@
         <v>88</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>117</v>
       </c>
       <c r="B118" s="3">
-        <v>21454</v>
+        <v>21451</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>133</v>
+        <v>430</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>118</v>
       </c>
       <c r="B119" s="3">
-        <v>21464</v>
+        <v>21453</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>7</v>
@@ -6407,46 +6458,46 @@
         <v>88</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>119</v>
       </c>
       <c r="B120" s="3">
-        <v>21465</v>
+        <v>21454</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>313</v>
+        <v>125</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>314</v>
+        <v>133</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>315</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>120</v>
       </c>
       <c r="B121" s="3">
-        <v>21470</v>
+        <v>21464</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>7</v>
@@ -6455,46 +6506,46 @@
         <v>88</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>121</v>
       </c>
       <c r="B122" s="3">
-        <v>21474</v>
+        <v>21465</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>110</v>
+        <v>313</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>70</v>
+        <v>314</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>191</v>
+        <v>315</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>122</v>
       </c>
       <c r="B123" s="3">
-        <v>21476</v>
+        <v>21470</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>7</v>
@@ -6503,22 +6554,22 @@
         <v>88</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>123</v>
       </c>
       <c r="B124" s="3">
-        <v>21477</v>
+        <v>21474</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>7</v>
@@ -6527,22 +6578,22 @@
         <v>88</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>124</v>
       </c>
       <c r="B125" s="3">
-        <v>21479</v>
+        <v>21476</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>417</v>
+        <v>136</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>329</v>
+        <v>68</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>7</v>
@@ -6551,22 +6602,22 @@
         <v>88</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>418</v>
+        <v>241</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>125</v>
       </c>
       <c r="B126" s="3">
-        <v>21484</v>
+        <v>21477</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>413</v>
+        <v>108</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>329</v>
+        <v>24</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>7</v>
@@ -6575,19 +6626,19 @@
         <v>88</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>414</v>
+        <v>263</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>126</v>
       </c>
       <c r="B127" s="3">
-        <v>21485</v>
+        <v>21479</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>329</v>
@@ -6599,22 +6650,22 @@
         <v>88</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>127</v>
       </c>
       <c r="B128" s="3">
-        <v>21488</v>
+        <v>21484</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>113</v>
+        <v>413</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>68</v>
+        <v>329</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>7</v>
@@ -6623,43 +6674,43 @@
         <v>88</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>244</v>
+        <v>414</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>128</v>
       </c>
       <c r="B129" s="3">
-        <v>21490</v>
+        <v>21485</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>118</v>
+        <v>405</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>119</v>
+        <v>329</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>169</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
-        <f t="shared" ref="A130:A193" si="2">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>129</v>
       </c>
       <c r="B130" s="3">
-        <v>21492</v>
+        <v>21488</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>68</v>
@@ -6671,46 +6722,46 @@
         <v>88</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>130</v>
       </c>
       <c r="B131" s="3">
-        <v>21494</v>
+        <v>21490</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>407</v>
+        <v>118</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>329</v>
+        <v>119</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>408</v>
+        <v>169</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>131</v>
       </c>
       <c r="B132" s="3">
-        <v>21495</v>
+        <v>21492</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>409</v>
+        <v>116</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>329</v>
+        <v>68</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>7</v>
@@ -6719,19 +6770,19 @@
         <v>88</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>410</v>
+        <v>243</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>132</v>
       </c>
       <c r="B133" s="3">
-        <v>21501</v>
+        <v>21494</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>329</v>
@@ -6743,22 +6794,22 @@
         <v>88</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>133</v>
       </c>
       <c r="B134" s="3">
-        <v>21502</v>
+        <v>21495</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>123</v>
+        <v>409</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>24</v>
+        <v>329</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>7</v>
@@ -6767,22 +6818,22 @@
         <v>88</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>248</v>
+        <v>410</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>134</v>
       </c>
       <c r="B135" s="3">
-        <v>21506</v>
+        <v>21501</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>246</v>
+        <v>415</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>24</v>
+        <v>329</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>7</v>
@@ -6791,22 +6842,22 @@
         <v>88</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>247</v>
+        <v>416</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>135</v>
       </c>
       <c r="B136" s="3">
-        <v>21507</v>
+        <v>21502</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>208</v>
+        <v>123</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>7</v>
@@ -6815,46 +6866,46 @@
         <v>88</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>136</v>
       </c>
       <c r="B137" s="3">
-        <v>21509</v>
+        <v>21506</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>158</v>
+        <v>247</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>137</v>
       </c>
       <c r="B138" s="3">
-        <v>21511</v>
+        <v>21507</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>7</v>
@@ -6863,46 +6914,46 @@
         <v>88</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>138</v>
       </c>
       <c r="B139" s="3">
-        <v>21515</v>
+        <v>21509</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>411</v>
+        <v>132</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>412</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>139</v>
       </c>
       <c r="B140" s="3">
-        <v>21517</v>
+        <v>21511</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>7</v>
@@ -6911,46 +6962,46 @@
         <v>88</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>140</v>
       </c>
       <c r="B141" s="3">
-        <v>21524</v>
+        <v>21515</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>128</v>
+        <v>411</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>129</v>
+        <v>329</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>173</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>141</v>
       </c>
       <c r="B142" s="3">
-        <v>21527</v>
+        <v>21517</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>331</v>
+        <v>135</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>7</v>
@@ -6959,46 +7010,46 @@
         <v>88</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>332</v>
+        <v>223</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>142</v>
       </c>
       <c r="B143" s="3">
-        <v>21528</v>
+        <v>21524</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>328</v>
+        <v>128</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>329</v>
+        <v>129</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>330</v>
+        <v>173</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>143</v>
       </c>
       <c r="B144" s="3">
-        <v>21556</v>
+        <v>21527</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>138</v>
+        <v>331</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>49</v>
+        <v>329</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>7</v>
@@ -7007,46 +7058,46 @@
         <v>88</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>219</v>
+        <v>332</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>144</v>
       </c>
       <c r="B145" s="3">
-        <v>21557</v>
+        <v>21528</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>145</v>
       </c>
       <c r="B146" s="3">
-        <v>21569</v>
+        <v>21553</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>286</v>
+        <v>472</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>7</v>
@@ -7055,22 +7106,22 @@
         <v>88</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>287</v>
+        <v>473</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>146</v>
       </c>
       <c r="B147" s="3">
-        <v>21577</v>
+        <v>21556</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>7</v>
@@ -7079,46 +7130,46 @@
         <v>88</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>147</v>
       </c>
       <c r="B148" s="3">
-        <v>21579</v>
+        <v>21557</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>333</v>
+        <v>399</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>335</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>148</v>
       </c>
       <c r="B149" s="3">
-        <v>21581</v>
+        <v>21563</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>147</v>
+        <v>474</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>7</v>
@@ -7127,94 +7178,94 @@
         <v>88</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>242</v>
+        <v>475</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>149</v>
       </c>
       <c r="B150" s="3">
-        <v>21584</v>
+        <v>21569</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>397</v>
+        <v>286</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>398</v>
+        <v>287</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>150</v>
       </c>
       <c r="B151" s="3">
-        <v>21587</v>
+        <v>21577</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>395</v>
+        <v>148</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>396</v>
+        <v>224</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>151</v>
       </c>
       <c r="B152" s="3">
-        <v>21588</v>
+        <v>21579</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>393</v>
+        <v>333</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>20</v>
+        <v>334</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>394</v>
+        <v>335</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>152</v>
       </c>
       <c r="B153" s="3">
-        <v>21593</v>
+        <v>21581</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>7</v>
@@ -7223,22 +7274,22 @@
         <v>88</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>153</v>
       </c>
       <c r="B154" s="3">
-        <v>21604</v>
+        <v>21584</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>318</v>
+        <v>397</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>10</v>
@@ -7247,22 +7298,22 @@
         <v>88</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>319</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>154</v>
       </c>
       <c r="B155" s="3">
-        <v>21607</v>
+        <v>21587</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>10</v>
@@ -7271,19 +7322,19 @@
         <v>88</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>155</v>
       </c>
       <c r="B156" s="3">
-        <v>21610</v>
+        <v>21588</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>20</v>
@@ -7295,46 +7346,46 @@
         <v>88</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>156</v>
       </c>
       <c r="B157" s="3">
-        <v>21612</v>
+        <v>21593</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G157" s="3">
-        <v>21612</v>
+      <c r="G157" s="3" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>157</v>
       </c>
       <c r="B158" s="3">
-        <v>21613</v>
+        <v>21604</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>10</v>
@@ -7343,22 +7394,22 @@
         <v>88</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>389</v>
+        <v>319</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>158</v>
       </c>
       <c r="B159" s="3">
-        <v>21614</v>
+        <v>21607</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>10</v>
@@ -7367,19 +7418,19 @@
         <v>88</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>159</v>
       </c>
       <c r="B160" s="3">
-        <v>21615</v>
+        <v>21610</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>20</v>
@@ -7391,118 +7442,118 @@
         <v>88</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>160</v>
       </c>
       <c r="B161" s="3">
-        <v>21616</v>
+        <v>21612</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>383</v>
+        <v>275</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G161" s="3" t="s">
-        <v>384</v>
+      <c r="G161" s="3">
+        <v>21612</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>161</v>
       </c>
       <c r="B162" s="3">
-        <v>21625</v>
+        <v>21613</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>162</v>
       </c>
       <c r="B163" s="3">
-        <v>21626</v>
+        <v>21614</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G163" s="3">
-        <v>21626</v>
+      <c r="G163" s="3" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>163</v>
       </c>
       <c r="B164" s="3">
-        <v>21630</v>
+        <v>21615</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>164</v>
       </c>
       <c r="B165" s="3">
-        <v>21631</v>
+        <v>21616</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>10</v>
@@ -7511,94 +7562,94 @@
         <v>88</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>310</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>165</v>
       </c>
       <c r="B166" s="3">
-        <v>21633</v>
+        <v>21619</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>268</v>
+        <v>464</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G166" s="3">
-        <v>21633</v>
+      <c r="G166" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>166</v>
       </c>
       <c r="B167" s="3">
-        <v>21634</v>
+        <v>21625</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>277</v>
+        <v>372</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>167</v>
       </c>
       <c r="B168" s="3">
-        <v>21644</v>
+        <v>21626</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G168" s="3" t="s">
-        <v>281</v>
+      <c r="G168" s="3">
+        <v>21626</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>168</v>
       </c>
       <c r="B169" s="3">
-        <v>21651</v>
+        <v>21630</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>250</v>
+        <v>369</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>7</v>
@@ -7607,118 +7658,118 @@
         <v>88</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>251</v>
+        <v>370</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>169</v>
       </c>
       <c r="B170" s="3">
-        <v>21657</v>
+        <v>21631</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>170</v>
       </c>
       <c r="B171" s="3">
-        <v>21661</v>
+        <v>21633</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G171" s="3" t="s">
-        <v>306</v>
+      <c r="G171" s="3">
+        <v>21633</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>171</v>
       </c>
       <c r="B172" s="3">
-        <v>21663</v>
+        <v>21634</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>343</v>
+        <v>276</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>344</v>
+        <v>277</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>172</v>
       </c>
       <c r="B173" s="3">
-        <v>21665</v>
+        <v>21644</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>173</v>
       </c>
       <c r="B174" s="3">
-        <v>21666</v>
+        <v>21651</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>7</v>
@@ -7727,46 +7778,46 @@
         <v>88</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>174</v>
       </c>
       <c r="B175" s="3">
-        <v>21671</v>
+        <v>21657</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>175</v>
       </c>
       <c r="B176" s="3">
-        <v>21672</v>
+        <v>21661</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>7</v>
@@ -7775,118 +7826,118 @@
         <v>88</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>176</v>
       </c>
       <c r="B177" s="3">
-        <v>21678</v>
+        <v>21663</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>289</v>
+        <v>344</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>177</v>
       </c>
       <c r="B178" s="3">
-        <v>21682</v>
+        <v>21665</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G178" s="3">
-        <v>21682</v>
+      <c r="G178" s="3" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>178</v>
       </c>
       <c r="B179" s="3">
-        <v>21695</v>
+        <v>21666</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>340</v>
+        <v>278</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G179" s="3">
-        <v>21695</v>
+      <c r="G179" s="3" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>179</v>
       </c>
       <c r="B180" s="3">
-        <v>21698</v>
+        <v>21671</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>180</v>
       </c>
       <c r="B181" s="3">
-        <v>21705</v>
+        <v>21672</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>7</v>
@@ -7895,22 +7946,22 @@
         <v>88</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>181</v>
       </c>
       <c r="B182" s="3">
-        <v>21713</v>
+        <v>21678</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>366</v>
+        <v>288</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>367</v>
+        <v>62</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>7</v>
@@ -7919,94 +7970,94 @@
         <v>88</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>368</v>
+        <v>289</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>182</v>
       </c>
       <c r="B183" s="3">
-        <v>21714</v>
+        <v>21682</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G183" s="3" t="s">
-        <v>317</v>
+      <c r="G183" s="3">
+        <v>21682</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>183</v>
       </c>
       <c r="B184" s="3">
-        <v>21716</v>
+        <v>21695</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G184" s="3" t="s">
-        <v>337</v>
+      <c r="G184" s="3">
+        <v>21695</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>184</v>
       </c>
       <c r="B185" s="3">
-        <v>21718</v>
+        <v>21698</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>432</v>
+        <v>303</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>433</v>
+        <v>304</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>185</v>
       </c>
       <c r="B186" s="3">
-        <v>21728</v>
+        <v>21700</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>347</v>
+        <v>458</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>7</v>
@@ -8015,22 +8066,22 @@
         <v>88</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>348</v>
+        <v>459</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>186</v>
       </c>
       <c r="B187" s="3">
-        <v>21736</v>
+        <v>21701</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>322</v>
+        <v>456</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>7</v>
@@ -8039,166 +8090,166 @@
         <v>88</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>323</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>187</v>
       </c>
       <c r="B188" s="3">
-        <v>21748</v>
+        <v>21705</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>188</v>
       </c>
       <c r="B189" s="3">
-        <v>21769</v>
+        <v>21713</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>421</v>
+        <v>366</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>9</v>
+        <v>367</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>189</v>
       </c>
       <c r="B190" s="3">
-        <v>21770</v>
+        <v>21714</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>190</v>
       </c>
       <c r="B191" s="3">
-        <v>21772</v>
+        <v>21716</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>191</v>
       </c>
       <c r="B192" s="3">
-        <v>21775</v>
+        <v>21718</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>358</v>
+        <v>432</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>359</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>192</v>
       </c>
       <c r="B193" s="3">
-        <v>21782</v>
+        <v>21728</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>446</v>
+        <v>347</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>447</v>
+        <v>348</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
-        <f t="shared" ref="A194:A210" si="3">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>193</v>
       </c>
       <c r="B194" s="3">
-        <v>21784</v>
+        <v>21736</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>379</v>
+        <v>322</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>7</v>
@@ -8207,70 +8258,70 @@
         <v>88</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>380</v>
+        <v>323</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>194</v>
       </c>
       <c r="B195" s="3">
-        <v>21787</v>
+        <v>21748</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>427</v>
+        <v>351</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>428</v>
+        <v>352</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>195</v>
       </c>
       <c r="B196" s="3">
-        <v>21789</v>
+        <v>21749</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>373</v>
+        <v>466</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>374</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>196</v>
       </c>
       <c r="B197" s="3">
-        <v>21792</v>
+        <v>21759</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>7</v>
@@ -8279,22 +8330,22 @@
         <v>88</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>197</v>
       </c>
       <c r="B198" s="3">
-        <v>21797</v>
+        <v>21760</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>364</v>
+        <v>490</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>7</v>
@@ -8303,19 +8354,19 @@
         <v>88</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>365</v>
+        <v>491</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>198</v>
       </c>
       <c r="B199" s="3">
-        <v>21802</v>
+        <v>21766</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>15</v>
@@ -8327,46 +8378,46 @@
         <v>88</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>199</v>
       </c>
       <c r="B200" s="3">
-        <v>21807</v>
+        <v>21769</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>200</v>
       </c>
       <c r="B201" s="3">
-        <v>21819</v>
+        <v>21770</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>425</v>
+        <v>356</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>367</v>
+        <v>24</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>7</v>
@@ -8375,94 +8426,94 @@
         <v>88</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>426</v>
+        <v>357</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>201</v>
       </c>
       <c r="B202" s="3">
-        <v>21829</v>
+        <v>21772</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>419</v>
+        <v>345</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>420</v>
+        <v>346</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>202</v>
       </c>
       <c r="B203" s="3">
-        <v>21836</v>
+        <v>21773</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>440</v>
+        <v>494</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>441</v>
+        <v>495</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>203</v>
       </c>
       <c r="B204" s="3">
-        <v>21837</v>
+        <v>21775</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>429</v>
+        <v>358</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>430</v>
+        <v>43</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>431</v>
+        <v>359</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>204</v>
       </c>
       <c r="B205" s="3">
-        <v>21839</v>
+        <v>21779</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>7</v>
@@ -8471,46 +8522,46 @@
         <v>88</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>424</v>
+        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>205</v>
       </c>
       <c r="B206" s="3">
-        <v>21840</v>
+        <v>21782</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>206</v>
       </c>
       <c r="B207" s="3">
-        <v>21850</v>
+        <v>21783</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>7</v>
@@ -8519,22 +8570,22 @@
         <v>88</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>207</v>
       </c>
       <c r="B208" s="3">
-        <v>21851</v>
+        <v>21784</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>7</v>
@@ -8543,70 +8594,70 @@
         <v>88</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>435</v>
+        <v>380</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>208</v>
       </c>
       <c r="B209" s="3">
-        <v>21864</v>
+        <v>21787</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
-        <f t="shared" si="3"/>
+        <f>ROW()-1</f>
         <v>209</v>
       </c>
       <c r="B210" s="3">
-        <v>21701</v>
+        <v>21788</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
-        <f t="shared" ref="A211:A217" si="4">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>210</v>
       </c>
       <c r="B211" s="3">
-        <v>21700</v>
+        <v>21789</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>458</v>
+        <v>373</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>7</v>
@@ -8615,67 +8666,67 @@
         <v>88</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>459</v>
+        <v>374</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
-        <f t="shared" si="4"/>
+        <f>ROW()-1</f>
         <v>211</v>
       </c>
       <c r="B212" s="3">
-        <v>21788</v>
+        <v>21792</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
-        <f t="shared" si="4"/>
+        <f>ROW()-1</f>
         <v>212</v>
       </c>
       <c r="B213" s="3">
-        <v>21817</v>
+        <v>21797</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>462</v>
+        <v>364</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>463</v>
+        <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
-        <f t="shared" si="4"/>
+        <f>ROW()-1</f>
         <v>213</v>
       </c>
       <c r="B214" s="3">
-        <v>21619</v>
+        <v>21802</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>15</v>
@@ -8687,46 +8738,46 @@
         <v>88</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
-        <f t="shared" si="4"/>
+        <f>ROW()-1</f>
         <v>214</v>
       </c>
       <c r="B215" s="3">
-        <v>21749</v>
+        <v>21807</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>466</v>
+        <v>377</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>467</v>
+        <v>378</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
-        <f t="shared" si="4"/>
+        <f>ROW()-1</f>
         <v>215</v>
       </c>
       <c r="B216" s="3">
-        <v>21766</v>
+        <v>21817</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>10</v>
@@ -8735,46 +8786,46 @@
         <v>88</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
-        <f t="shared" si="4"/>
+        <f>ROW()-1</f>
         <v>216</v>
       </c>
       <c r="B217" s="3">
-        <v>21863</v>
+        <v>21819</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>84</v>
+        <v>367</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>471</v>
+        <v>426</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
-        <f t="shared" ref="A218:A223" si="5">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>217</v>
       </c>
       <c r="B218" s="3">
-        <v>21553</v>
+        <v>21829</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>472</v>
+        <v>419</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>7</v>
@@ -8783,22 +8834,22 @@
         <v>88</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>473</v>
+        <v>420</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
-        <f t="shared" si="5"/>
+        <f>ROW()-1</f>
         <v>218</v>
       </c>
       <c r="B219" s="3">
-        <v>21563</v>
+        <v>21836</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>7</v>
@@ -8807,99 +8858,267 @@
         <v>88</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
-        <f t="shared" si="5"/>
+        <f>ROW()-1</f>
         <v>219</v>
       </c>
       <c r="B220" s="3">
-        <v>21075</v>
+        <v>21837</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>46</v>
+        <v>430</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>477</v>
+        <v>431</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
-        <f t="shared" si="5"/>
+        <f>ROW()-1</f>
         <v>220</v>
       </c>
       <c r="B221" s="3">
-        <v>21858</v>
+        <v>21839</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>478</v>
+        <v>423</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>479</v>
+        <v>424</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
-        <f t="shared" si="5"/>
+        <f>ROW()-1</f>
         <v>221</v>
       </c>
       <c r="B222" s="3">
-        <v>10509</v>
+        <v>21840</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>64</v>
+        <v>430</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="18" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
-        <f t="shared" si="5"/>
+        <f>ROW()-1</f>
         <v>222</v>
       </c>
-      <c r="B223" s="3"/>
-      <c r="C223" s="3"/>
-      <c r="D223" s="3"/>
-      <c r="E223" s="3"/>
-      <c r="F223" s="3"/>
-      <c r="G223" s="3"/>
+      <c r="B223" s="3">
+        <v>21850</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A224" s="3">
+        <f>ROW()-1</f>
+        <v>223</v>
+      </c>
+      <c r="B224" s="3">
+        <v>21851</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A225" s="3">
+        <f>ROW()-1</f>
+        <v>224</v>
+      </c>
+      <c r="B225" s="3">
+        <v>21858</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A226" s="3">
+        <f>ROW()-1</f>
+        <v>225</v>
+      </c>
+      <c r="B226" s="3">
+        <v>21863</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A227" s="3">
+        <f>ROW()-1</f>
+        <v>226</v>
+      </c>
+      <c r="B227" s="3">
+        <v>21864</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A228" s="3">
+        <f>ROW()-1</f>
+        <v>227</v>
+      </c>
+      <c r="B228" s="3">
+        <v>21877</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A229" s="3">
+        <f>ROW()-1</f>
+        <v>228</v>
+      </c>
+      <c r="B229" s="3">
+        <v>21883</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A230" s="3">
+        <f>ROW()-1</f>
+        <v>229</v>
+      </c>
+      <c r="B230" s="3"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
+      <c r="E230" s="3"/>
+      <c r="F230" s="3"/>
+      <c r="G230" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B223">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="B2:B230">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8965,7 +9184,7 @@
       </c>
       <c r="D2" s="23">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.0497737556561094E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="25">
@@ -8981,7 +9200,7 @@
       </c>
       <c r="I2" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>2.7149321266968326E-2</v>
+        <v>2.6315789473684209E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -8998,7 +9217,7 @@
       </c>
       <c r="D3" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.2624434389140271E-2</v>
+        <v>2.1929824561403508E-2</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="25">
@@ -9014,7 +9233,7 @@
       </c>
       <c r="I3" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>9.0497737556561094E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9031,7 +9250,7 @@
       </c>
       <c r="D4" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>7.2398190045248875E-2</v>
+        <v>7.0175438596491224E-2</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="25">
@@ -9047,7 +9266,7 @@
       </c>
       <c r="I4" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9064,7 +9283,7 @@
       </c>
       <c r="D5" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.0497737556561094E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="25">
@@ -9076,11 +9295,11 @@
       </c>
       <c r="H5" s="2">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.19909502262443438</v>
+        <v>0.19736842105263158</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9097,7 +9316,7 @@
       </c>
       <c r="D6" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8099547511312219E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="25">
@@ -9113,7 +9332,7 @@
       </c>
       <c r="I6" s="16">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8099547511312219E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9130,7 +9349,7 @@
       </c>
       <c r="D7" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="7">
@@ -9146,7 +9365,7 @@
       </c>
       <c r="I7" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10859728506787331</v>
+        <v>0.10526315789473684</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9163,7 +9382,7 @@
       </c>
       <c r="D8" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="7">
@@ -9175,11 +9394,11 @@
       </c>
       <c r="H8" s="8">
         <f>COUNTIF(Table1[نوع الجهة],Table2[[#This Row],[نوع الجهة]])</f>
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I8" s="19">
         <f>Table2[[#This Row],[عدد الخدمات]]/Table2[[#Totals],[عدد الخدمات]]</f>
-        <v>0.6244343891402715</v>
+        <v>0.63157894736842102</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.3">
@@ -9196,7 +9415,7 @@
       </c>
       <c r="D9" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="26"/>
@@ -9205,7 +9424,7 @@
       </c>
       <c r="H9" s="17">
         <f>SUBTOTAL(109,Table2[عدد الخدمات])</f>
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I9" s="21"/>
     </row>
@@ -9223,7 +9442,7 @@
       </c>
       <c r="D10" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>5.8823529411764705E-2</v>
+        <v>5.701754385964912E-2</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="25"/>
@@ -9241,11 +9460,11 @@
       </c>
       <c r="C11" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="9" t="s">
@@ -9275,7 +9494,7 @@
       </c>
       <c r="D12" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.0497737556561094E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="12">
@@ -9290,7 +9509,7 @@
       </c>
       <c r="I12" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>7.6923076923076927E-2</v>
+        <v>7.4561403508771926E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9307,7 +9526,7 @@
       </c>
       <c r="D13" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="12">
@@ -9318,11 +9537,11 @@
       </c>
       <c r="H13" s="13">
         <f>COUNTIF(Table1[نوع العمل],Table4[[#This Row],[نوع العمل]])</f>
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="I13" s="15">
         <f>Table4[[#This Row],[عدد الخدمات]]/Table4[[#Totals],[عدد الخدمات]]</f>
-        <v>0.92307692307692313</v>
+        <v>0.92543859649122806</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
@@ -9339,7 +9558,7 @@
       </c>
       <c r="D14" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.0497737556561094E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="12"/>
@@ -9348,7 +9567,7 @@
       </c>
       <c r="H14" s="13">
         <f>SUBTOTAL(109,Table4[عدد الخدمات])</f>
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -9366,7 +9585,7 @@
       </c>
       <c r="D15" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
       <c r="E15" s="18"/>
     </row>
@@ -9384,7 +9603,7 @@
       </c>
       <c r="D16" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>7.2398190045248875E-2</v>
+        <v>7.0175438596491224E-2</v>
       </c>
       <c r="E16" s="18"/>
     </row>
@@ -9402,7 +9621,7 @@
       </c>
       <c r="D17" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
       <c r="E17" s="18"/>
     </row>
@@ -9420,7 +9639,7 @@
       </c>
       <c r="D18" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
       <c r="E18" s="18"/>
     </row>
@@ -9438,7 +9657,7 @@
       </c>
       <c r="D19" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8099547511312219E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
       <c r="E19" s="18"/>
     </row>
@@ -9456,7 +9675,7 @@
       </c>
       <c r="D20" s="24">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
       <c r="E20" s="18"/>
     </row>
@@ -9474,7 +9693,7 @@
       </c>
       <c r="D21" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.0497737556561094E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
       <c r="E21" s="18"/>
     </row>
@@ -9492,7 +9711,7 @@
       </c>
       <c r="D22" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
       <c r="E22" s="18"/>
     </row>
@@ -9510,7 +9729,7 @@
       </c>
       <c r="D23" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.1674208144796379E-2</v>
+        <v>3.0701754385964911E-2</v>
       </c>
       <c r="E23" s="18"/>
     </row>
@@ -9528,7 +9747,7 @@
       </c>
       <c r="D24" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.7149321266968326E-2</v>
+        <v>2.6315789473684209E-2</v>
       </c>
       <c r="E24" s="18"/>
     </row>
@@ -9546,7 +9765,7 @@
       </c>
       <c r="D25" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>3.6199095022624438E-2</v>
+        <v>3.5087719298245612E-2</v>
       </c>
       <c r="E25" s="18"/>
     </row>
@@ -9560,11 +9779,11 @@
       </c>
       <c r="C26" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D26" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.9547511312217188E-2</v>
+        <v>0.10964912280701754</v>
       </c>
       <c r="E26" s="18"/>
     </row>
@@ -9582,7 +9801,7 @@
       </c>
       <c r="D27" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
       <c r="E27" s="18"/>
     </row>
@@ -9600,7 +9819,7 @@
       </c>
       <c r="D28" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.072398190045249E-2</v>
+        <v>3.9473684210526314E-2</v>
       </c>
       <c r="E28" s="18"/>
     </row>
@@ -9618,7 +9837,7 @@
       </c>
       <c r="D29" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>2.2624434389140271E-2</v>
+        <v>2.1929824561403508E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" x14ac:dyDescent="0.3">
@@ -9631,11 +9850,11 @@
       </c>
       <c r="C30" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8099547511312219E-2</v>
+        <v>2.1929824561403508E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.3">
@@ -9648,11 +9867,11 @@
       </c>
       <c r="C31" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" x14ac:dyDescent="0.3">
@@ -9665,11 +9884,11 @@
       </c>
       <c r="C32" s="8">
         <f>COUNTIF(Table1[جهة الخدمة],Table3[[#This Row],[اسم الجهة]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.8099547511312219E-2</v>
+        <v>2.1929824561403508E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9686,7 +9905,7 @@
       </c>
       <c r="D33" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>1.3574660633484163E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9703,7 +9922,7 @@
       </c>
       <c r="D34" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280542E-2</v>
+        <v>4.3859649122807015E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9720,7 +9939,7 @@
       </c>
       <c r="D35" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>9.0497737556561094E-3</v>
+        <v>8.771929824561403E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9737,7 +9956,7 @@
       </c>
       <c r="D36" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9754,7 +9973,7 @@
       </c>
       <c r="D37" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.072398190045249E-2</v>
+        <v>3.9473684210526314E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9771,7 +9990,7 @@
       </c>
       <c r="D38" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.072398190045249E-2</v>
+        <v>3.9473684210526314E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9788,7 +10007,7 @@
       </c>
       <c r="D39" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280542E-2</v>
+        <v>4.3859649122807015E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9805,7 +10024,7 @@
       </c>
       <c r="D40" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>4.5248868778280547E-3</v>
+        <v>4.3859649122807015E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9822,7 +10041,7 @@
       </c>
       <c r="D41" s="19">
         <f>Table3[[#This Row],[عدد الخدمات]]/Table3[[#Totals],[عدد الخدمات]]</f>
-        <v>0.10407239819004525</v>
+        <v>0.10087719298245613</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -9832,11 +10051,11 @@
       </c>
       <c r="C42" s="8">
         <f>SUBTOTAL(109,Table3[عدد الخدمات])</f>
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D42" s="20">
         <f>SUBTOTAL(109,Table3[النسبة المئوية])</f>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
     </row>
   </sheetData>
